--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">kit</t>
   </si>
@@ -20,28 +20,31 @@
     <t xml:space="preserve">channels</t>
   </si>
   <si>
-    <t xml:space="preserve">sample_repeats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pko_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pko_repeats</t>
+    <t xml:space="preserve">pko_wt_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pko_h_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pko_m_name</t>
   </si>
   <si>
     <t xml:space="preserve">oko_name</t>
   </si>
   <si>
-    <t xml:space="preserve">oko_repeats</t>
-  </si>
-  <si>
     <t xml:space="preserve">SNP-A</t>
   </si>
   <si>
     <t xml:space="preserve">FAM/HEX</t>
   </si>
   <si>
-    <t xml:space="preserve">ПКО SNP-A</t>
+    <t xml:space="preserve">ПКО_wt SNP-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО_h SNP-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО_m SNP-A</t>
   </si>
   <si>
     <t xml:space="preserve">ОКО SNP-A</t>
@@ -50,7 +53,13 @@
     <t xml:space="preserve">SNP-B</t>
   </si>
   <si>
-    <t xml:space="preserve">ПКО SNP-B</t>
+    <t xml:space="preserve">ПКО_wt SNP-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО_h SNP-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО_m SNP-B</t>
   </si>
   <si>
     <t xml:space="preserve">ОКО SNP-B</t>
@@ -401,54 +410,45 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -1,82 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Blagodatskikh.KA\Documents\PClaneR\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="930" yWindow="0" windowWidth="13125" windowHeight="6105"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">kit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">channels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pko_wt_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pko_h_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pko_m_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oko_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAM/HEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКО_wt SNP-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКО_h SNP-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКО_m SNP-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОКО SNP-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКО_wt SNP-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКО_h SNP-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКО_m SNP-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОКО SNP-B</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+  <si>
+    <t>kit</t>
+  </si>
+  <si>
+    <t>channels</t>
+  </si>
+  <si>
+    <t>pko_wt_name</t>
+  </si>
+  <si>
+    <t>pko_h_name</t>
+  </si>
+  <si>
+    <t>pko_m_name</t>
+  </si>
+  <si>
+    <t>oko_name</t>
+  </si>
+  <si>
+    <t>FAM/HEX</t>
+  </si>
+  <si>
+    <t>С414</t>
+  </si>
+  <si>
+    <t>С355</t>
+  </si>
+  <si>
+    <t>С223</t>
+  </si>
+  <si>
+    <t>ПКО 1 T/T</t>
+  </si>
+  <si>
+    <t>ПКО 2 T/C</t>
+  </si>
+  <si>
+    <t>ПКО 3 C/C</t>
+  </si>
+  <si>
+    <t>ОКО К-</t>
+  </si>
+  <si>
+    <t>ПКО 1 C/C</t>
+  </si>
+  <si>
+    <t>ПКО 2 C/T</t>
+  </si>
+  <si>
+    <t>ПКО 3 T/T</t>
+  </si>
+  <si>
+    <t>ПКО 1 С/С</t>
+  </si>
+  <si>
+    <t>ПКО 2 С/A</t>
+  </si>
+  <si>
+    <t>ПКО 3 A/A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -99,13 +121,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -387,11 +419,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,48 +443,68 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -1,104 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Blagodatskikh.KA\Documents\PClaneR\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="0" windowWidth="13125" windowHeight="6105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <si>
-    <t>kit</t>
-  </si>
-  <si>
-    <t>channels</t>
-  </si>
-  <si>
-    <t>pko_wt_name</t>
-  </si>
-  <si>
-    <t>pko_h_name</t>
-  </si>
-  <si>
-    <t>pko_m_name</t>
-  </si>
-  <si>
-    <t>oko_name</t>
-  </si>
-  <si>
-    <t>FAM/HEX</t>
-  </si>
-  <si>
-    <t>С414</t>
-  </si>
-  <si>
-    <t>С355</t>
-  </si>
-  <si>
-    <t>С223</t>
-  </si>
-  <si>
-    <t>ПКО 1 T/T</t>
-  </si>
-  <si>
-    <t>ПКО 2 T/C</t>
-  </si>
-  <si>
-    <t>ПКО 3 C/C</t>
-  </si>
-  <si>
-    <t>ОКО К-</t>
-  </si>
-  <si>
-    <t>ПКО 1 C/C</t>
-  </si>
-  <si>
-    <t>ПКО 2 C/T</t>
-  </si>
-  <si>
-    <t>ПКО 3 T/T</t>
-  </si>
-  <si>
-    <t>ПКО 1 С/С</t>
-  </si>
-  <si>
-    <t>ПКО 2 С/A</t>
-  </si>
-  <si>
-    <t>ПКО 3 A/A</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t xml:space="preserve">kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">channels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pko_wt_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pko_h_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pko_m_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oko_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM/HEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 1 T/T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 2 T/C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 3 C/C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОКО К-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 1 C/C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 2 C/T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 3 T/T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 1 С/С</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 2 С/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКО 3 A/A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,23 +108,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -419,11 +396,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,68 +420,68 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
+    <row r="4">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
+      <c r="F4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>